--- a/artfynd/A 48442-2022 artfynd.xlsx
+++ b/artfynd/A 48442-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48442-2022 artfynd.xlsx
+++ b/artfynd/A 48442-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98323259</v>
+        <v>98323257</v>
       </c>
       <c r="B2" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,7 +715,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597102.7542937483</v>
+        <v>597103</v>
       </c>
       <c r="R2" t="n">
-        <v>6378070.513662701</v>
+        <v>6378070</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -762,24 +757,14 @@
           <t>2020-06-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ekoxeuppropet 2020. krypande</t>
+          <t>Ekoxeuppropet 2020. kanske död</t>
         </is>
       </c>
       <c r="AD2" t="b">
